--- a/PCB/BOM FPGA_DENDY SE.xlsx
+++ b/PCB/BOM FPGA_DENDY SE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="112">
   <si>
     <t>SN74LVC8T245PWR</t>
   </si>
@@ -344,6 +344,15 @@
   </si>
   <si>
     <t>TO-92</t>
+  </si>
+  <si>
+    <t>crystal oscillator  14.318MHz</t>
+  </si>
+  <si>
+    <t>crystal oscillator  17.734MHz</t>
+  </si>
+  <si>
+    <t>7050</t>
   </si>
 </sst>
 </file>
@@ -4529,7 +4538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:U56"/>
+  <dimension ref="A4:U58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -5029,94 +5038,86 @@
       <c r="T21" s="39"/>
       <c r="U21" s="39"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1">
+    <row r="22" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36">
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1206</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
+      <c r="E22" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="36"/>
+      <c r="G22" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" s="6"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
+    <row r="23" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36">
+        <v>1</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="36"/>
+      <c r="G23" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="39"/>
+      <c r="U23" s="39"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1206</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
@@ -5135,31 +5136,43 @@
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
-        <v>7</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>45</v>
+        <v>2</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="20" t="s">
-        <v>44</v>
+      <c r="H25" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="I25" s="6"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>39</v>
@@ -5167,82 +5180,74 @@
       <c r="G26" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="H26" s="20" t="s">
-        <v>46</v>
+      <c r="H26" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="I26" s="6"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="I28" s="6"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
@@ -5251,7 +5256,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="5"/>
@@ -5265,86 +5270,86 @@
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
     </row>
-    <row r="30" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36">
-        <v>1</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="36" t="s">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1">
+        <v>4</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="37" t="s">
+      <c r="G30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="I30" s="38"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
-      <c r="N30" s="37"/>
-      <c r="O30" s="37"/>
-      <c r="P30" s="37"/>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="37"/>
-      <c r="S30" s="37"/>
+      <c r="H30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="6"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
     </row>
-    <row r="31" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="37" t="s">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H31" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31" s="38"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
+      <c r="H31" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" s="6"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
     </row>
     <row r="32" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="36"/>
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
       <c r="D32" s="36">
-        <v>6</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>69</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>9</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I32" s="38"/>
       <c r="J32" s="37"/>
@@ -5358,74 +5363,77 @@
       <c r="R32" s="37"/>
       <c r="S32" s="37"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1">
+    <row r="33" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="36"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36">
+        <v>1</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33" s="38"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="37"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="37"/>
+    </row>
+    <row r="34" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="36"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36">
         <v>6</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="E34" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G34" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H33" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I33" s="6"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" s="6"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
+      <c r="H34" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="38"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37"/>
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>55</v>
@@ -5433,28 +5441,39 @@
       <c r="G35" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="H35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" s="6"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="5"/>
@@ -5469,175 +5488,186 @@
       <c r="S36" s="5"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
       <c r="D37" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37" s="6"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
+      <c r="H37" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
-        <v>2</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>95</v>
+      <c r="H38" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="I38" s="6"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="F39" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H39" s="32" t="s">
-        <v>100</v>
+      <c r="H39" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="I39" s="6"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
     </row>
-    <row r="40" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36">
-        <v>1</v>
-      </c>
-      <c r="E40" s="33" t="s">
-        <v>105</v>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>96</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H40" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="I40" s="38"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="39"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="39"/>
-      <c r="U40" s="39"/>
+      <c r="H40" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I40" s="6"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
       <c r="D41" s="1">
-        <v>36</v>
-      </c>
-      <c r="E41" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F41" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="H41" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="I41" s="6"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
       <c r="D42" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F42" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>102</v>
-      </c>
+      <c r="H42" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="38"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="39"/>
+      <c r="S42" s="39"/>
+      <c r="T42" s="39"/>
+      <c r="U42" s="39"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>20</v>
+      <c r="D43" s="1">
+        <v>36</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>15</v>
@@ -5645,91 +5675,68 @@
       <c r="G43" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="14"/>
-      <c r="U43" s="2"/>
+      <c r="H43" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1">
-        <v>9</v>
-      </c>
-      <c r="E44" s="40" t="s">
-        <v>72</v>
+    <row r="44" spans="1:21" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D44" s="36">
+        <v>3</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>101</v>
       </c>
       <c r="F44" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I44" s="6"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
+      <c r="G44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C45" s="7"/>
-      <c r="D45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>74</v>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I45" s="13"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="14"/>
+      <c r="U45" s="2"/>
     </row>
-    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B46" s="1"/>
-      <c r="D46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F46" s="34" t="s">
-        <v>82</v>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1">
+        <v>9</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="36" t="s">
+        <v>15</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I46" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="I46" s="6"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
@@ -5740,37 +5747,55 @@
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
-      <c r="U46" s="2"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5"/>
-      <c r="U47" s="2"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I47" s="13"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="D48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>81</v>
+      </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
@@ -5784,10 +5809,12 @@
       <c r="S48" s="5"/>
       <c r="U48" s="2"/>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="21"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="22"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -5803,7 +5830,9 @@
       <c r="S49" s="5"/>
       <c r="U49" s="2"/>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="22"/>
@@ -5822,10 +5851,10 @@
       <c r="S50" s="5"/>
       <c r="U50" s="2"/>
     </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="22"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="21"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -5839,68 +5868,66 @@
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
+      <c r="U51" s="2"/>
     </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="U52" s="2"/>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C53" s="4"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
     </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C54" s="4"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7"/>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="7"/>
-      <c r="T54" s="4"/>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
+      <c r="D55" s="8"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -5918,25 +5945,65 @@
       <c r="S55" s="4"/>
       <c r="T55" s="4"/>
     </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C56" s="4"/>
       <c r="D56" s="7"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
       <c r="T56" s="4"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C58" s="4"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
